--- a/InputData/elec/RM/Reserve Margin.xlsx
+++ b/InputData/elec/RM/Reserve Margin.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\RM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/RM/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2316F12-EA26-8944-B357-8BFC5B4FA841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="75" windowWidth="22995" windowHeight="11580"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="RM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -61,7 +75,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -99,13 +113,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -124,9 +137,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,9 +177,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -201,7 +214,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -236,7 +249,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,16 +422,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -426,42 +439,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>2015</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -473,17 +486,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:BE2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -595,117 +608,257 @@
       <c r="AK1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL1">
+        <v>2051</v>
+      </c>
+      <c r="AM1">
+        <v>2052</v>
+      </c>
+      <c r="AN1">
+        <v>2053</v>
+      </c>
+      <c r="AO1">
+        <v>2054</v>
+      </c>
+      <c r="AP1">
+        <v>2055</v>
+      </c>
+      <c r="AQ1">
+        <v>2056</v>
+      </c>
+      <c r="AR1">
+        <v>2057</v>
+      </c>
+      <c r="AS1">
+        <v>2058</v>
+      </c>
+      <c r="AT1">
+        <v>2059</v>
+      </c>
+      <c r="AU1">
+        <v>2060</v>
+      </c>
+      <c r="AV1">
+        <v>2061</v>
+      </c>
+      <c r="AW1">
+        <v>2062</v>
+      </c>
+      <c r="AX1">
+        <v>2063</v>
+      </c>
+      <c r="AY1">
+        <v>2064</v>
+      </c>
+      <c r="AZ1">
+        <v>2065</v>
+      </c>
+      <c r="BA1">
+        <v>2066</v>
+      </c>
+      <c r="BB1">
+        <v>2067</v>
+      </c>
+      <c r="BC1">
+        <v>2068</v>
+      </c>
+      <c r="BD1">
+        <v>2069</v>
+      </c>
+      <c r="BE1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="K2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="O2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="U2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="V2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="W2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="X2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AD2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AE2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AG2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AH2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AI2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AJ2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AK2" s="3">
+      <c r="B2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="C2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="D2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="E2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="G2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="H2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="J2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="K2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="L2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="N2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="P2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="R2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="S2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="T2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="U2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="V2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="X2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Y2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Z2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AA2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AC2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AF2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AG2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AH2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AK2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AL2">
+        <f>AK2</f>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" ref="AM2:BE2" si="0">AL2</f>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="BD2">
+        <f t="shared" si="0"/>
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="BE2">
+        <f t="shared" si="0"/>
         <v>0.14119999999999999</v>
       </c>
     </row>
